--- a/ipar40tk-server/backend/baselines/mid-rpm_high-stress_filled.xlsx
+++ b/ipar40tk-server/backend/baselines/mid-rpm_high-stress_filled.xlsx
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -59,7 +59,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -92,7 +92,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
